--- a/output/graficos_dimensiones/comunal_d_env_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:17</t>
+    <t xml:space="preserve">2026-09-10 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:31</t>
+    <t xml:space="preserve">2026-09-12 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_la araucania.xlsx
@@ -48,21 +48,21 @@
     <t xml:space="preserve">Toltén</t>
   </si>
   <si>
+    <t xml:space="preserve">Freire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipeuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cunco</t>
   </si>
   <si>
-    <t xml:space="preserve">Freire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipeuco</t>
+    <t xml:space="preserve">Los Sauces</t>
   </si>
   <si>
     <t xml:space="preserve">Traiguén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Sauces</t>
-  </si>
-  <si>
     <t xml:space="preserve">Victoria</t>
   </si>
   <si>
@@ -99,12 +99,12 @@
     <t xml:space="preserve">Temuco</t>
   </si>
   <si>
+    <t xml:space="preserve">Renaico</t>
+  </si>
+  <si>
     <t xml:space="preserve">Collipulli</t>
   </si>
   <si>
-    <t xml:space="preserve">Renaico</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curarrehue</t>
   </si>
   <si>
@@ -123,12 +123,12 @@
     <t xml:space="preserve">Vilcún</t>
   </si>
   <si>
+    <t xml:space="preserve">Pucón</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ercilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Pucón</t>
-  </si>
-  <si>
     <t xml:space="preserve">Padre Las Casas</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:42</t>
+    <t xml:space="preserve">2026-09-24 00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -574,7 +574,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>148.06</v>
+        <v>159.88</v>
       </c>
     </row>
     <row r="3">
@@ -591,7 +591,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>146.03</v>
+        <v>158.07</v>
       </c>
     </row>
     <row r="4">
@@ -608,7 +608,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>139.83</v>
+        <v>151.01</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +625,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>137.53</v>
+        <v>148.89</v>
       </c>
     </row>
     <row r="6">
@@ -636,13 +636,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>9103</v>
+        <v>9105</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>137.17</v>
+        <v>148.18</v>
       </c>
     </row>
     <row r="7">
@@ -653,13 +653,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>9105</v>
+        <v>9110</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>137.04</v>
+        <v>147.73</v>
       </c>
     </row>
     <row r="8">
@@ -670,13 +670,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>9110</v>
+        <v>9103</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>136.79</v>
+        <v>147.46</v>
       </c>
     </row>
     <row r="9">
@@ -687,13 +687,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>9210</v>
+        <v>9206</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>132.84</v>
+        <v>144.1</v>
       </c>
     </row>
     <row r="10">
@@ -704,13 +704,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>9206</v>
+        <v>9210</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>132.3</v>
+        <v>144.05</v>
       </c>
     </row>
     <row r="11">
@@ -727,7 +727,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>131.19</v>
+        <v>140.81</v>
       </c>
     </row>
     <row r="12">
@@ -744,7 +744,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>129.22</v>
+        <v>139.05</v>
       </c>
     </row>
     <row r="13">
@@ -761,7 +761,7 @@
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>128.86</v>
+        <v>138.57</v>
       </c>
     </row>
     <row r="14">
@@ -778,7 +778,7 @@
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>127.78</v>
+        <v>138.28</v>
       </c>
     </row>
     <row r="15">
@@ -795,7 +795,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>124.01</v>
+        <v>134.03</v>
       </c>
     </row>
     <row r="16">
@@ -812,7 +812,7 @@
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>122.81</v>
+        <v>132.67</v>
       </c>
     </row>
     <row r="17">
@@ -829,7 +829,7 @@
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>119.99</v>
+        <v>130.63</v>
       </c>
     </row>
     <row r="18">
@@ -846,7 +846,7 @@
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>119.07</v>
+        <v>128.61</v>
       </c>
     </row>
     <row r="19">
@@ -863,7 +863,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>113.37</v>
+        <v>122.65</v>
       </c>
     </row>
     <row r="20">
@@ -880,7 +880,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>111.29</v>
+        <v>120.19</v>
       </c>
     </row>
     <row r="21">
@@ -897,7 +897,7 @@
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>108.1</v>
+        <v>116.33</v>
       </c>
     </row>
     <row r="22">
@@ -914,7 +914,7 @@
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>104.34</v>
+        <v>112.04</v>
       </c>
     </row>
     <row r="23">
@@ -925,13 +925,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>9202</v>
+        <v>9209</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>103.07</v>
+        <v>111.63</v>
       </c>
     </row>
     <row r="24">
@@ -942,13 +942,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>9209</v>
+        <v>9202</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>103.03</v>
+        <v>111.11</v>
       </c>
     </row>
     <row r="25">
@@ -965,7 +965,7 @@
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>101.19</v>
+        <v>107.59</v>
       </c>
     </row>
     <row r="26">
@@ -982,7 +982,7 @@
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>98.97</v>
+        <v>105.36</v>
       </c>
     </row>
     <row r="27">
@@ -999,7 +999,7 @@
         <v>2021</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>97.84</v>
+        <v>104.71</v>
       </c>
     </row>
     <row r="28">
@@ -1016,7 +1016,7 @@
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>97.66</v>
+        <v>104.33</v>
       </c>
     </row>
     <row r="29">
@@ -1033,7 +1033,7 @@
         <v>2021</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>96.68</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="30">
@@ -1050,7 +1050,7 @@
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>93.54</v>
+        <v>101.12</v>
       </c>
     </row>
     <row r="31">
@@ -1061,13 +1061,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>9204</v>
+        <v>9115</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>86.54</v>
+        <v>93.31</v>
       </c>
     </row>
     <row r="32">
@@ -1078,13 +1078,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>9115</v>
+        <v>9204</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>86.46</v>
+        <v>92.83</v>
       </c>
     </row>
     <row r="33">
@@ -1101,7 +1101,7 @@
         <v>2021</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>84.72</v>
+        <v>91.65</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:11</t>
+    <t xml:space="preserve">2026-10-02 16:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:26</t>
+    <t xml:space="preserve">2026-10-05 16:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
